--- a/testing/appium/reports/Mobile_E2E_Report_31_Tests.xlsx
+++ b/testing/appium/reports/Mobile_E2E_Report_31_Tests.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="359">
   <si>
     <t>Execution Date</t>
   </si>
@@ -43,7 +43,7 @@
     <t>Execution Duration</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.665Z</t>
+    <t>2026-06-16T09:30:56.136Z</t>
   </si>
   <si>
     <t>Android Devices</t>
@@ -55,7 +55,7 @@
     <t>100.00%</t>
   </si>
   <si>
-    <t>1s</t>
+    <t>0s</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -97,13 +97,13 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.171Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.183Z</t>
-  </si>
-  <si>
-    <t>12ms</t>
+    <t>2026-06-16T09:30:55.671Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.689Z</t>
+  </si>
+  <si>
+    <t>18ms</t>
   </si>
   <si>
     <t>TC-2</t>
@@ -112,244 +112,253 @@
     <t>Validate Invalid Email Format</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.197Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.202Z</t>
+    <t>2026-06-16T09:30:55.697Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.706Z</t>
+  </si>
+  <si>
+    <t>9ms</t>
+  </si>
+  <si>
+    <t>TC-3</t>
+  </si>
+  <si>
+    <t>Validate Valid Email Accepted</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.712Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.719Z</t>
+  </si>
+  <si>
+    <t>7ms</t>
+  </si>
+  <si>
+    <t>TC-4</t>
+  </si>
+  <si>
+    <t>Validate Phone Number Length</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.725Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.734Z</t>
+  </si>
+  <si>
+    <t>TC-5</t>
+  </si>
+  <si>
+    <t>Validate Password Complexity</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.747Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.755Z</t>
+  </si>
+  <si>
+    <t>8ms</t>
+  </si>
+  <si>
+    <t>TC-6</t>
+  </si>
+  <si>
+    <t>Validate Maximum Length</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.767Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.792Z</t>
+  </si>
+  <si>
+    <t>25ms</t>
+  </si>
+  <si>
+    <t>TC-7</t>
+  </si>
+  <si>
+    <t>Validate Date Field Required</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.810Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.816Z</t>
+  </si>
+  <si>
+    <t>6ms</t>
+  </si>
+  <si>
+    <t>TC-8</t>
+  </si>
+  <si>
+    <t>Authentication Testing</t>
+  </si>
+  <si>
+    <t>Validate empty username</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.827Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.837Z</t>
+  </si>
+  <si>
+    <t>10ms</t>
+  </si>
+  <si>
+    <t>TC-9</t>
+  </si>
+  <si>
+    <t>Validate empty password</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.848Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.864Z</t>
+  </si>
+  <si>
+    <t>16ms</t>
+  </si>
+  <si>
+    <t>TC-10</t>
+  </si>
+  <si>
+    <t>Validate invalid credentials</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.871Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.879Z</t>
+  </si>
+  <si>
+    <t>TC-11</t>
+  </si>
+  <si>
+    <t>Validate successful login</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.884Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.893Z</t>
+  </si>
+  <si>
+    <t>TC-12</t>
+  </si>
+  <si>
+    <t>Validate logout functionality</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.903Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.912Z</t>
+  </si>
+  <si>
+    <t>TC-13</t>
+  </si>
+  <si>
+    <t>Navigation &amp; Gesture Testing</t>
+  </si>
+  <si>
+    <t>Navigate to Home via Bottom Nav</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.920Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.926Z</t>
+  </si>
+  <si>
+    <t>TC-14</t>
+  </si>
+  <si>
+    <t>Navigate to Profile via Bottom Nav</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.932Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.936Z</t>
+  </si>
+  <si>
+    <t>4ms</t>
+  </si>
+  <si>
+    <t>TC-15</t>
+  </si>
+  <si>
+    <t>Navigate to Settings via Bottom Nav</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.940Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.951Z</t>
+  </si>
+  <si>
+    <t>11ms</t>
+  </si>
+  <si>
+    <t>TC-16</t>
+  </si>
+  <si>
+    <t>Open Navigation Drawer</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.956Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.963Z</t>
+  </si>
+  <si>
+    <t>TC-17</t>
+  </si>
+  <si>
+    <t>Close Navigation Drawer</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.971Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.976Z</t>
   </si>
   <si>
     <t>5ms</t>
   </si>
   <si>
-    <t>TC-3</t>
-  </si>
-  <si>
-    <t>Validate Valid Email Accepted</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.214Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.252Z</t>
-  </si>
-  <si>
-    <t>38ms</t>
-  </si>
-  <si>
-    <t>TC-4</t>
-  </si>
-  <si>
-    <t>Validate Phone Number Length</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.264Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.268Z</t>
-  </si>
-  <si>
-    <t>4ms</t>
-  </si>
-  <si>
-    <t>TC-5</t>
-  </si>
-  <si>
-    <t>Validate Password Complexity</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.285Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.288Z</t>
+    <t>TC-18</t>
+  </si>
+  <si>
+    <t>Switch to Tab 1</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.980Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.983Z</t>
   </si>
   <si>
     <t>3ms</t>
   </si>
   <si>
-    <t>TC-6</t>
-  </si>
-  <si>
-    <t>Validate Maximum Length</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.314Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.317Z</t>
-  </si>
-  <si>
-    <t>TC-7</t>
-  </si>
-  <si>
-    <t>Validate Date Field Required</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.337Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.343Z</t>
-  </si>
-  <si>
-    <t>TC-8</t>
-  </si>
-  <si>
-    <t>Authentication Testing</t>
-  </si>
-  <si>
-    <t>Validate empty username</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.349Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.374Z</t>
-  </si>
-  <si>
-    <t>25ms</t>
-  </si>
-  <si>
-    <t>TC-9</t>
-  </si>
-  <si>
-    <t>Validate empty password</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.408Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.413Z</t>
-  </si>
-  <si>
-    <t>TC-10</t>
-  </si>
-  <si>
-    <t>Validate invalid credentials</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.419Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.445Z</t>
-  </si>
-  <si>
-    <t>26ms</t>
-  </si>
-  <si>
-    <t>TC-11</t>
-  </si>
-  <si>
-    <t>Validate successful login</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.448Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.451Z</t>
-  </si>
-  <si>
-    <t>TC-12</t>
-  </si>
-  <si>
-    <t>Validate logout functionality</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.452Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.459Z</t>
-  </si>
-  <si>
-    <t>7ms</t>
-  </si>
-  <si>
-    <t>TC-13</t>
-  </si>
-  <si>
-    <t>Navigation &amp; Gesture Testing</t>
-  </si>
-  <si>
-    <t>Navigate to Home via Bottom Nav</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.463Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.465Z</t>
-  </si>
-  <si>
-    <t>2ms</t>
-  </si>
-  <si>
-    <t>TC-14</t>
-  </si>
-  <si>
-    <t>Navigate to Profile via Bottom Nav</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.467Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.469Z</t>
-  </si>
-  <si>
-    <t>TC-15</t>
-  </si>
-  <si>
-    <t>Navigate to Settings via Bottom Nav</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.474Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.477Z</t>
-  </si>
-  <si>
-    <t>TC-16</t>
-  </si>
-  <si>
-    <t>Open Navigation Drawer</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.481Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.483Z</t>
-  </si>
-  <si>
-    <t>TC-17</t>
-  </si>
-  <si>
-    <t>Close Navigation Drawer</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.486Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.489Z</t>
-  </si>
-  <si>
-    <t>TC-18</t>
-  </si>
-  <si>
-    <t>Switch to Tab 1</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.495Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.498Z</t>
-  </si>
-  <si>
     <t>TC-19</t>
   </si>
   <si>
     <t>Switch to Tab 2</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.501Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.505Z</t>
+    <t>2026-06-16T09:30:55.988Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.998Z</t>
   </si>
   <si>
     <t>TC-20</t>
@@ -361,13 +370,10 @@
     <t>Validate Buttons Clickable</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.508Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.509Z</t>
-  </si>
-  <si>
-    <t>1ms</t>
+    <t>2026-06-16T09:30:56.005Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.009Z</t>
   </si>
   <si>
     <t>TC-21</t>
@@ -376,10 +382,10 @@
     <t>Validate Text Fields Input</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.512Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.513Z</t>
+    <t>2026-06-16T09:30:56.013Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.018Z</t>
   </si>
   <si>
     <t>TC-22</t>
@@ -388,10 +394,10 @@
     <t>Validate Checkbox Checked State</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.555Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.557Z</t>
+    <t>2026-06-16T09:30:56.023Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.027Z</t>
   </si>
   <si>
     <t>TC-23</t>
@@ -400,10 +406,10 @@
     <t>Validate Checkbox Unchecked State</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.560Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.562Z</t>
+    <t>2026-06-16T09:30:56.032Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.036Z</t>
   </si>
   <si>
     <t>TC-24</t>
@@ -412,10 +418,10 @@
     <t>Validate Radio Button Selection</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.573Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.575Z</t>
+    <t>2026-06-16T09:30:56.042Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.048Z</t>
   </si>
   <si>
     <t>TC-25</t>
@@ -424,13 +430,10 @@
     <t>Validate Dropdown Selection</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.610Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.625Z</t>
-  </si>
-  <si>
-    <t>15ms</t>
+    <t>2026-06-16T09:30:56.054Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.061Z</t>
   </si>
   <si>
     <t>TC-26</t>
@@ -439,10 +442,10 @@
     <t>Validate RecyclerView Card Tap</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.627Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.629Z</t>
+    <t>2026-06-16T09:30:56.065Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.071Z</t>
   </si>
   <si>
     <t>TC-27</t>
@@ -451,10 +454,10 @@
     <t>Validate Dialog Accept Action</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.632Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.634Z</t>
+    <t>2026-06-16T09:30:56.078Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.083Z</t>
   </si>
   <si>
     <t>TC-28</t>
@@ -463,10 +466,10 @@
     <t>Validate Dialog Dismiss Action</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.647Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.650Z</t>
+    <t>2026-06-16T09:30:56.090Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.095Z</t>
   </si>
   <si>
     <t>TC-29</t>
@@ -475,10 +478,10 @@
     <t>Validate Toast Message Appearance</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.654Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.656Z</t>
+    <t>2026-06-16T09:30:56.105Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.110Z</t>
   </si>
   <si>
     <t>TC-30</t>
@@ -487,10 +490,10 @@
     <t>Validate Snackbar Text</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.659Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.660Z</t>
+    <t>2026-06-16T09:30:56.116Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.119Z</t>
   </si>
   <si>
     <t>TC-31</t>
@@ -499,10 +502,10 @@
     <t>Validate Progress Bar State</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.662Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.663Z</t>
+    <t>2026-06-16T09:30:56.126Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.133Z</t>
   </si>
   <si>
     <t>Test Name</t>
@@ -529,6 +532,9 @@
     <t>Remarks</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.669Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~submit_button</t>
   </si>
   <si>
@@ -538,73 +544,61 @@
     <t>Element displayed</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.174Z</t>
-  </si>
-  <si>
     <t>Click element: ~submit_button</t>
   </si>
   <si>
     <t>Clicked successfully</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.176Z</t>
+    <t>2026-06-16T09:30:55.674Z</t>
   </si>
   <si>
     <t>Wait for element: ~error_msg</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.177Z</t>
-  </si>
-  <si>
     <t>Get text from element: ~error_msg</t>
   </si>
   <si>
     <t>Text retrieved: 'Welcome Username is required Password is required Invalid credentials Invalid email Valid email accepted Invalid phone number Password must contain a number Max length exceeded Date is required Home Screen Profile Screen Settings Screen Drawer Opened Drawer Closed Tab 1 Active Tab 2 Active Checked Unchecked Option A Selected Dropdown Value Card Tapped Dialog Accepted Dialog Dismissed Toast Message Snackbar Text Progress 50% Test Input'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.189Z</t>
-  </si>
-  <si>
     <t>Wait for element: ~email_input</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.190Z</t>
-  </si>
-  <si>
     <t>Set value for element: ~email_input</t>
   </si>
   <si>
     <t>Value set to 'invalid-email'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.191Z</t>
+    <t>2026-06-16T09:30:55.703Z</t>
   </si>
   <si>
     <t>Text retrieved: 'Welcome Username is required Password is required Invalid credentials Invalid email Valid email accepted Invalid phone number Password must contain a number Max length exceeded Date is required Home Screen Profile Screen Settings Screen Drawer Opened Drawer Closed Tab 1 Active Tab 2 Active Checked Unchecked Option A Selected Dropdown Value Card Tapped Dialog Accepted Dialog Dismissed Toast Message Snackbar Text Progress 50% invalid-email'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.242Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.244Z</t>
+    <t>2026-06-16T09:30:55.714Z</t>
   </si>
   <si>
     <t>Value set to 'test@example.com'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.245Z</t>
+    <t>2026-06-16T09:30:55.716Z</t>
   </si>
   <si>
     <t>Wait for element: ~success_msg</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.717Z</t>
+  </si>
+  <si>
     <t>Get text from element: ~success_msg</t>
   </si>
   <si>
     <t>Text retrieved: 'Welcome Username is required Password is required Invalid credentials Invalid email Valid email accepted Invalid phone number Password must contain a number Max length exceeded Date is required Home Screen Profile Screen Settings Screen Drawer Opened Drawer Closed Tab 1 Active Tab 2 Active Checked Unchecked Option A Selected Dropdown Value Card Tapped Dialog Accepted Dialog Dismissed Toast Message Snackbar Text Progress 50% test@example.com'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.266Z</t>
+    <t>2026-06-16T09:30:55.724Z</t>
   </si>
   <si>
     <t>Wait for element: ~phone_input</t>
@@ -616,49 +610,58 @@
     <t>Value set to '123'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.267Z</t>
+    <t>2026-06-16T09:30:55.727Z</t>
   </si>
   <si>
     <t>Text retrieved: 'Welcome Username is required Password is required Invalid credentials Invalid email Valid email accepted Invalid phone number Password must contain a number Max length exceeded Date is required Home Screen Profile Screen Settings Screen Drawer Opened Drawer Closed Tab 1 Active Tab 2 Active Checked Unchecked Option A Selected Dropdown Value Card Tapped Dialog Accepted Dialog Dismissed Toast Message Snackbar Text Progress 50% 123'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.283Z</t>
+    <t>2026-06-16T09:30:55.748Z</t>
   </si>
   <si>
     <t>Wait for element: ~password_input</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.749Z</t>
+  </si>
+  <si>
     <t>Set value for element: ~password_input</t>
   </si>
   <si>
     <t>Value set to 'password'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.284Z</t>
+    <t>2026-06-16T09:30:55.751Z</t>
   </si>
   <si>
     <t>Text retrieved: 'Welcome Username is required Password is required Invalid credentials Invalid email Valid email accepted Invalid phone number Password must contain a number Max length exceeded Date is required Home Screen Profile Screen Settings Screen Drawer Opened Drawer Closed Tab 1 Active Tab 2 Active Checked Unchecked Option A Selected Dropdown Value Card Tapped Dialog Accepted Dialog Dismissed Toast Message Snackbar Text Progress 50% password'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.293Z</t>
+    <t>2026-06-16T09:30:55.765Z</t>
   </si>
   <si>
     <t>Wait for element: ~username_input</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.771Z</t>
+  </si>
+  <si>
     <t>Set value for element: ~username_input</t>
   </si>
   <si>
     <t>Value set to 'thisisaverylongusernamethatexceedsmaxlength'</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.785Z</t>
+  </si>
+  <si>
     <t>Text retrieved: 'Welcome Username is required Password is required Invalid credentials Invalid email Valid email accepted Invalid phone number Password must contain a number Max length exceeded Date is required Home Screen Profile Screen Settings Screen Drawer Opened Drawer Closed Tab 1 Active Tab 2 Active Checked Unchecked Option A Selected Dropdown Value Card Tapped Dialog Accepted Dialog Dismissed Toast Message Snackbar Text Progress 50% thisisaverylongusernamethatexceedsmaxlength'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.322Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.324Z</t>
+    <t>2026-06-16T09:30:55.812Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.814Z</t>
   </si>
   <si>
     <t>Wait for element: ~date_error</t>
@@ -667,19 +670,19 @@
     <t>Get text from element: ~date_error</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.348Z</t>
-  </si>
-  <si>
     <t>Value set to 'password123'</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.829Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~login_button</t>
   </si>
   <si>
     <t>Click element: ~login_button</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.372Z</t>
+    <t>2026-06-16T09:30:55.833Z</t>
   </si>
   <si>
     <t>Wait for element: ~error_message</t>
@@ -691,88 +694,94 @@
     <t>Text retrieved: 'Welcome Username is required Password is required Invalid credentials Invalid email Valid email accepted Invalid phone number Password must contain a number Max length exceeded Date is required Home Screen Profile Screen Settings Screen Drawer Opened Drawer Closed Tab 1 Active Tab 2 Active Checked Unchecked Option A Selected Dropdown Value Card Tapped Dialog Accepted Dialog Dismissed Toast Message Snackbar Text Progress 50% password123'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.409Z</t>
-  </si>
-  <si>
     <t>Value set to 'testuser'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.410Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.411Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.412Z</t>
+    <t>2026-06-16T09:30:55.857Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.860Z</t>
   </si>
   <si>
     <t>Text retrieved: 'Welcome Username is required Password is required Invalid credentials Invalid email Valid email accepted Invalid phone number Password must contain a number Max length exceeded Date is required Home Screen Profile Screen Settings Screen Drawer Opened Drawer Closed Tab 1 Active Tab 2 Active Checked Unchecked Option A Selected Dropdown Value Card Tapped Dialog Accepted Dialog Dismissed Toast Message Snackbar Text Progress 50% testuser'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.440Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.441Z</t>
-  </si>
-  <si>
     <t>Value set to 'invalidUser'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.442Z</t>
+    <t>2026-06-16T09:30:55.872Z</t>
   </si>
   <si>
     <t>Value set to 'wrongPass'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.443Z</t>
+    <t>2026-06-16T09:30:55.874Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.875Z</t>
   </si>
   <si>
     <t>Text retrieved: 'Welcome Username is required Password is required Invalid credentials Invalid email Valid email accepted Invalid phone number Password must contain a number Max length exceeded Date is required Home Screen Profile Screen Settings Screen Drawer Opened Drawer Closed Tab 1 Active Tab 2 Active Checked Unchecked Option A Selected Dropdown Value Card Tapped Dialog Accepted Dialog Dismissed Toast Message Snackbar Text Progress 50% wrongPass'</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.885Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.886Z</t>
+  </si>
+  <si>
     <t>Value set to 'validUser'</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.887Z</t>
+  </si>
+  <si>
     <t>Value set to 'validPass'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.449Z</t>
+    <t>2026-06-16T09:30:55.889Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.890Z</t>
   </si>
   <si>
     <t>Wait for element: ~welcome_text</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.450Z</t>
-  </si>
-  <si>
     <t>Get text from element: ~welcome_text</t>
   </si>
   <si>
     <t>Text retrieved: 'Welcome Username is required Password is required Invalid credentials Invalid email Valid email accepted Invalid phone number Password must contain a number Max length exceeded Date is required Home Screen Profile Screen Settings Screen Drawer Opened Drawer Closed Tab 1 Active Tab 2 Active Checked Unchecked Option A Selected Dropdown Value Card Tapped Dialog Accepted Dialog Dismissed Toast Message Snackbar Text Progress 50% validPass'</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.456Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.457Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.458Z</t>
+    <t>2026-06-16T09:30:55.905Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.907Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.908Z</t>
   </si>
   <si>
     <t>Wait for element: ~logout_button</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.909Z</t>
+  </si>
+  <si>
     <t>Click element: ~logout_button</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.921Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~nav_home</t>
   </si>
   <si>
     <t>Click element: ~nav_home</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.464Z</t>
+    <t>2026-06-16T09:30:55.924Z</t>
   </si>
   <si>
     <t>Wait for element: ~screen_title</t>
@@ -781,7 +790,7 @@
     <t>Get text from element: ~screen_title</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.468Z</t>
+    <t>2026-06-16T09:30:55.933Z</t>
   </si>
   <si>
     <t>Wait for element: ~nav_profile</t>
@@ -790,16 +799,25 @@
     <t>Click element: ~nav_profile</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.475Z</t>
+    <t>2026-06-16T09:30:55.934Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.944Z</t>
   </si>
   <si>
     <t>Wait for element: ~nav_settings</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.945Z</t>
+  </si>
+  <si>
     <t>Click element: ~nav_settings</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.476Z</t>
+    <t>2026-06-16T09:30:55.950Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:55.957Z</t>
   </si>
   <si>
     <t>Wait for element: ~hamburger_menu</t>
@@ -808,7 +826,7 @@
     <t>Click element: ~hamburger_menu</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.482Z</t>
+    <t>2026-06-16T09:30:55.961Z</t>
   </si>
   <si>
     <t>Wait for element: ~drawer_state</t>
@@ -817,16 +835,16 @@
     <t>Get text from element: ~drawer_state</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.972Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~close_drawer</t>
   </si>
   <si>
     <t>Click element: ~close_drawer</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.488Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.493Z</t>
+    <t>2026-06-16T09:30:55.974Z</t>
   </si>
   <si>
     <t>Wait for element: ~tab_1</t>
@@ -835,13 +853,19 @@
     <t>Click element: ~tab_1</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.981Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~tab_content</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:55.982Z</t>
+  </si>
+  <si>
     <t>Get text from element: ~tab_content</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.502Z</t>
+    <t>2026-06-16T09:30:55.994Z</t>
   </si>
   <si>
     <t>Wait for element: ~tab_2</t>
@@ -850,7 +874,10 @@
     <t>Click element: ~tab_2</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.503Z</t>
+    <t>2026-06-16T09:30:55.996Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.006Z</t>
   </si>
   <si>
     <t>Wait for element: ~sample_button</t>
@@ -859,6 +886,9 @@
     <t>Click element: ~sample_button</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:56.014Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~sample_text_field</t>
   </si>
   <si>
@@ -868,10 +898,16 @@
     <t>Value set to 'Test Input'</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:56.015Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.016Z</t>
+  </si>
+  <si>
     <t>Get text from element: ~sample_text_field</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.530Z</t>
+    <t>2026-06-16T09:30:56.024Z</t>
   </si>
   <si>
     <t>Wait for element: ~checkbox_1</t>
@@ -880,7 +916,7 @@
     <t>Click element: ~checkbox_1</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.531Z</t>
+    <t>2026-06-16T09:30:56.025Z</t>
   </si>
   <si>
     <t>Wait for element: ~checkbox_status</t>
@@ -889,7 +925,7 @@
     <t>Get text from element: ~checkbox_status</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.561Z</t>
+    <t>2026-06-16T09:30:56.030Z</t>
   </si>
   <si>
     <t>Wait for element: ~checkbox_2</t>
@@ -898,7 +934,10 @@
     <t>Click element: ~checkbox_2</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.568Z</t>
+    <t>2026-06-16T09:30:56.033Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.044Z</t>
   </si>
   <si>
     <t>Wait for element: ~radio_option_A</t>
@@ -907,46 +946,46 @@
     <t>Click element: ~radio_option_A</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.569Z</t>
+    <t>2026-06-16T09:30:56.045Z</t>
   </si>
   <si>
     <t>Wait for element: ~radio_status</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:56.046Z</t>
+  </si>
+  <si>
     <t>Get text from element: ~radio_status</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.599Z</t>
-  </si>
-  <si>
     <t>Wait for element: ~dropdown</t>
   </si>
   <si>
     <t>Click element: ~dropdown</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.603Z</t>
+    <t>2026-06-16T09:30:56.057Z</t>
   </si>
   <si>
     <t>Wait for element: ~dropdown_value</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.604Z</t>
-  </si>
-  <si>
     <t>Click element: ~dropdown_value</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:56.058Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~dropdown_status</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.605Z</t>
+    <t>2026-06-16T09:30:56.059Z</t>
   </si>
   <si>
     <t>Get text from element: ~dropdown_status</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.628Z</t>
+    <t>2026-06-16T09:30:56.068Z</t>
   </si>
   <si>
     <t>Wait for element: ~recycler_card_1</t>
@@ -955,19 +994,28 @@
     <t>Click element: ~recycler_card_1</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:56.069Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~card_status</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:56.070Z</t>
+  </si>
+  <si>
     <t>Get text from element: ~card_status</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:56.075Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~open_dialog</t>
   </si>
   <si>
     <t>Click element: ~open_dialog</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.633Z</t>
+    <t>2026-06-16T09:30:56.076Z</t>
   </si>
   <si>
     <t>Wait for element: ~dialog_ok</t>
@@ -976,16 +1024,19 @@
     <t>Click element: ~dialog_ok</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:56.077Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~dialog_status</t>
   </si>
   <si>
     <t>Get text from element: ~dialog_status</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.648Z</t>
-  </si>
-  <si>
-    <t>2026-06-15T07:53:39.649Z</t>
+    <t>2026-06-16T09:30:56.091Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.092Z</t>
   </si>
   <si>
     <t>Wait for element: ~dialog_cancel</t>
@@ -994,7 +1045,10 @@
     <t>Click element: ~dialog_cancel</t>
   </si>
   <si>
-    <t>2026-06-15T07:53:39.653Z</t>
+    <t>2026-06-16T09:30:56.094Z</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.107Z</t>
   </si>
   <si>
     <t>Wait for element: ~trigger_toast</t>
@@ -1003,22 +1057,34 @@
     <t>Click element: ~trigger_toast</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:56.108Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~toast_container</t>
   </si>
   <si>
     <t>Get text from element: ~toast_container</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:56.117Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~trigger_snackbar</t>
   </si>
   <si>
     <t>Click element: ~trigger_snackbar</t>
   </si>
   <si>
+    <t>2026-06-16T09:30:56.118Z</t>
+  </si>
+  <si>
     <t>Wait for element: ~snackbar_container</t>
   </si>
   <si>
     <t>Get text from element: ~snackbar_container</t>
+  </si>
+  <si>
+    <t>2026-06-16T09:30:56.130Z</t>
   </si>
   <si>
     <t>Wait for element: ~progress_bar</t>
@@ -1614,18 +1680,18 @@
         <v>43</v>
       </c>
       <c r="H5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D6" t="s">
         <v>25</v>
@@ -1634,24 +1700,24 @@
         <v>26</v>
       </c>
       <c r="F6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G6" t="s">
         <v>47</v>
       </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>48</v>
-      </c>
-      <c r="H6" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" t="s">
         <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D7" t="s">
         <v>25</v>
@@ -1660,13 +1726,13 @@
         <v>26</v>
       </c>
       <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" t="s">
         <v>52</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>53</v>
-      </c>
-      <c r="H7" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -1692,18 +1758,18 @@
         <v>57</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
         <v>25</v>
@@ -1712,24 +1778,24 @@
         <v>26</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H9" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D10" t="s">
         <v>25</v>
@@ -1738,24 +1804,24 @@
         <v>26</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G10" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
         <v>25</v>
@@ -1764,24 +1830,24 @@
         <v>26</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
         <v>25</v>
@@ -1790,24 +1856,24 @@
         <v>26</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D13" t="s">
         <v>25</v>
@@ -1816,13 +1882,13 @@
         <v>26</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H13" t="s">
-        <v>81</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1848,18 +1914,18 @@
         <v>86</v>
       </c>
       <c r="H14" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
         <v>83</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
         <v>25</v>
@@ -1868,13 +1934,13 @@
         <v>26</v>
       </c>
       <c r="F15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" t="s">
         <v>90</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>91</v>
-      </c>
-      <c r="H15" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -1900,18 +1966,18 @@
         <v>95</v>
       </c>
       <c r="H16" t="s">
-        <v>49</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
         <v>83</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
@@ -1920,24 +1986,24 @@
         <v>26</v>
       </c>
       <c r="F17" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H17" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
         <v>83</v>
       </c>
       <c r="C18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D18" t="s">
         <v>25</v>
@@ -1946,24 +2012,24 @@
         <v>26</v>
       </c>
       <c r="F18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G18" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B19" t="s">
         <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
         <v>25</v>
@@ -1972,24 +2038,24 @@
         <v>26</v>
       </c>
       <c r="F19" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G19" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H19" t="s">
-        <v>49</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B20" t="s">
         <v>83</v>
       </c>
       <c r="C20" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D20" t="s">
         <v>25</v>
@@ -1998,24 +2064,24 @@
         <v>26</v>
       </c>
       <c r="F20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="G20" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="H20" t="s">
-        <v>44</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D21" t="s">
         <v>25</v>
@@ -2024,24 +2090,24 @@
         <v>26</v>
       </c>
       <c r="F21" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="G21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H21" t="s">
-        <v>117</v>
+        <v>91</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B22" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D22" t="s">
         <v>25</v>
@@ -2050,24 +2116,24 @@
         <v>26</v>
       </c>
       <c r="F22" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G22" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B23" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C23" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
         <v>25</v>
@@ -2076,24 +2142,24 @@
         <v>26</v>
       </c>
       <c r="F23" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G23" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H23" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D24" t="s">
         <v>25</v>
@@ -2102,24 +2168,24 @@
         <v>26</v>
       </c>
       <c r="F24" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G24" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H24" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B25" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D25" t="s">
         <v>25</v>
@@ -2128,24 +2194,24 @@
         <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G25" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="H25" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B26" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C26" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D26" t="s">
         <v>25</v>
@@ -2154,24 +2220,24 @@
         <v>26</v>
       </c>
       <c r="F26" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G26" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H26" t="s">
-        <v>138</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D27" t="s">
         <v>25</v>
@@ -2180,24 +2246,24 @@
         <v>26</v>
       </c>
       <c r="F27" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G27" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H27" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C28" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D28" t="s">
         <v>25</v>
@@ -2206,24 +2272,24 @@
         <v>26</v>
       </c>
       <c r="F28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G28" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H28" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B29" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C29" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D29" t="s">
         <v>25</v>
@@ -2232,24 +2298,24 @@
         <v>26</v>
       </c>
       <c r="F29" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G29" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H29" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B30" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C30" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D30" t="s">
         <v>25</v>
@@ -2258,24 +2324,24 @@
         <v>26</v>
       </c>
       <c r="F30" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G30" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H30" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B31" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C31" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D31" t="s">
         <v>25</v>
@@ -2284,24 +2350,24 @@
         <v>26</v>
       </c>
       <c r="F31" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G31" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H31" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B32" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C32" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D32" t="s">
         <v>25</v>
@@ -2310,13 +2376,13 @@
         <v>26</v>
       </c>
       <c r="F32" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G32" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H32" t="s">
-        <v>117</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2340,13 +2406,13 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B1" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D1" t="s">
         <v>17</v>
@@ -2355,7 +2421,7 @@
         <v>2</v>
       </c>
       <c r="F1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2377,75 +2443,75 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>172</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>174</v>
+        <v>27</v>
       </c>
       <c r="B3" t="s">
         <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
@@ -2454,7 +2520,7 @@
         <v>180</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E5" t="s">
         <v>181</v>
@@ -2462,58 +2528,58 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>182</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
         <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>184</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D7" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E7" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -2522,134 +2588,134 @@
         <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B10" t="s">
         <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E10" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B11" t="s">
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D11" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E11" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B12" t="s">
         <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D12" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E12" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B13" t="s">
         <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B14" t="s">
         <v>41</v>
       </c>
       <c r="C14" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s">
         <v>41</v>
       </c>
       <c r="C15" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D15" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E15" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B16" t="s">
         <v>41</v>
       </c>
       <c r="C16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D16" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E16" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B17" t="s">
         <v>41</v>
@@ -2658,27 +2724,27 @@
         <v>180</v>
       </c>
       <c r="D17" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E17" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D18" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E18" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -2686,81 +2752,81 @@
         <v>202</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" t="s">
+        <v>174</v>
+      </c>
+      <c r="E19" t="s">
         <v>204</v>
-      </c>
-      <c r="D19" t="s">
-        <v>172</v>
-      </c>
-      <c r="E19" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D20" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E20" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" t="s">
         <v>180</v>
       </c>
       <c r="D21" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E21" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>207</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
         <v>208</v>
       </c>
-      <c r="B22" t="s">
-        <v>51</v>
-      </c>
-      <c r="C22" t="s">
-        <v>209</v>
-      </c>
       <c r="D22" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E22" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
         <v>210</v>
       </c>
       <c r="D23" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E23" t="s">
         <v>211</v>
@@ -2768,101 +2834,101 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D24" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E24" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
         <v>180</v>
       </c>
       <c r="D25" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E25" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s">
         <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D26" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E26" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B27" t="s">
         <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D27" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E27" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B28" t="s">
         <v>55</v>
       </c>
       <c r="C28" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B29" t="s">
         <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E29" t="s">
         <v>181</v>
@@ -2870,33 +2936,33 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>217</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D30" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E30" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>217</v>
+        <v>62</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D31" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E31" t="s">
         <v>218</v>
@@ -2904,101 +2970,101 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>219</v>
+      </c>
+      <c r="B32" t="s">
         <v>61</v>
       </c>
-      <c r="B32" t="s">
-        <v>60</v>
-      </c>
       <c r="C32" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D32" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E32" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>219</v>
+      </c>
+      <c r="B33" t="s">
         <v>61</v>
       </c>
-      <c r="B33" t="s">
-        <v>60</v>
-      </c>
       <c r="C33" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D33" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E33" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D34" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E34" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B35" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D35" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E35" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>225</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C36" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D36" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>225</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C37" t="s">
         <v>210</v>
       </c>
       <c r="D37" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E37" t="s">
         <v>226</v>
@@ -3009,33 +3075,33 @@
         <v>227</v>
       </c>
       <c r="B38" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C38" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D38" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E38" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B39" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C39" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D39" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E39" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -3043,200 +3109,200 @@
         <v>228</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C40" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D40" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E40" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>228</v>
+      </c>
+      <c r="B41" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" t="s">
+        <v>224</v>
+      </c>
+      <c r="D41" t="s">
+        <v>174</v>
+      </c>
+      <c r="E41" t="s">
         <v>229</v>
-      </c>
-      <c r="B41" t="s">
-        <v>65</v>
-      </c>
-      <c r="C41" t="s">
-        <v>223</v>
-      </c>
-      <c r="D41" t="s">
-        <v>172</v>
-      </c>
-      <c r="E41" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>231</v>
+        <v>72</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C42" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E42" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>232</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C43" t="s">
         <v>210</v>
       </c>
       <c r="D43" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E43" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B44" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C44" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D44" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C45" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D45" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E45" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B46" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C46" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D46" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E46" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B47" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C47" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D47" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E47" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B48" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C48" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D48" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E48" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C49" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D49" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E49" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>236</v>
+      </c>
+      <c r="B50" t="s">
         <v>75</v>
       </c>
-      <c r="B50" t="s">
-        <v>74</v>
-      </c>
       <c r="C50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D50" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E50" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>237</v>
+      </c>
+      <c r="B51" t="s">
         <v>75</v>
-      </c>
-      <c r="B51" t="s">
-        <v>74</v>
       </c>
       <c r="C51" t="s">
         <v>210</v>
       </c>
       <c r="D51" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E51" t="s">
         <v>238</v>
@@ -3244,87 +3310,87 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>239</v>
+      </c>
+      <c r="B52" t="s">
         <v>75</v>
       </c>
-      <c r="B52" t="s">
-        <v>74</v>
-      </c>
       <c r="C52" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D52" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E52" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>239</v>
+      </c>
+      <c r="B53" t="s">
         <v>75</v>
       </c>
-      <c r="B53" t="s">
-        <v>74</v>
-      </c>
       <c r="C53" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D53" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E53" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C54" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E54" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B55" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C55" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D55" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E55" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C56" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="D56" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E56" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -3332,47 +3398,47 @@
         <v>242</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C57" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D57" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E57" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C58" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D58" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E58" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C59" t="s">
         <v>210</v>
       </c>
       <c r="D59" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E59" t="s">
         <v>238</v>
@@ -3380,19 +3446,19 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C60" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D60" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E60" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -3400,166 +3466,166 @@
         <v>246</v>
       </c>
       <c r="B61" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C61" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D61" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E61" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C62" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D62" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E62" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C63" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D63" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E63" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B64" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C64" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C65" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D65" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E65" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C66" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E66" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>85</v>
+        <v>252</v>
       </c>
       <c r="B67" t="s">
         <v>84</v>
       </c>
       <c r="C67" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="D67" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E67" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>85</v>
+        <v>252</v>
       </c>
       <c r="B68" t="s">
         <v>84</v>
       </c>
       <c r="C68" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D68" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E68" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B69" t="s">
         <v>84</v>
       </c>
       <c r="C69" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D69" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E69" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B70" t="s">
         <v>84</v>
       </c>
       <c r="C70" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D70" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E70" t="s">
         <v>181</v>
@@ -3567,67 +3633,67 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C71" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E71" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B72" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C72" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D72" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E72" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B73" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C73" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D73" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E73" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B74" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C74" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D74" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E74" t="s">
         <v>181</v>
@@ -3635,67 +3701,67 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B75" t="s">
         <v>93</v>
       </c>
       <c r="C75" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E75" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B76" t="s">
         <v>93</v>
       </c>
       <c r="C76" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D76" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E76" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B77" t="s">
         <v>93</v>
       </c>
       <c r="C77" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D77" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E77" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="B78" t="s">
         <v>93</v>
       </c>
       <c r="C78" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D78" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E78" t="s">
         <v>181</v>
@@ -3703,67 +3769,67 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>267</v>
+      </c>
+      <c r="B79" t="s">
         <v>98</v>
       </c>
-      <c r="B79" t="s">
-        <v>97</v>
-      </c>
       <c r="C79" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D79" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>267</v>
+      </c>
+      <c r="B80" t="s">
         <v>98</v>
       </c>
-      <c r="B80" t="s">
-        <v>97</v>
-      </c>
       <c r="C80" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="D80" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B81" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C81" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D81" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E81" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B82" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C82" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D82" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E82" t="s">
         <v>181</v>
@@ -3771,67 +3837,67 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>273</v>
+      </c>
+      <c r="B83" t="s">
         <v>102</v>
       </c>
-      <c r="B83" t="s">
-        <v>101</v>
-      </c>
       <c r="C83" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="D83" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E83" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>273</v>
+      </c>
+      <c r="B84" t="s">
         <v>102</v>
       </c>
-      <c r="B84" t="s">
-        <v>101</v>
-      </c>
       <c r="C84" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="D84" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E84" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B85" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C85" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="D85" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E85" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B86" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C86" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D86" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E86" t="s">
         <v>181</v>
@@ -3839,67 +3905,67 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>270</v>
+        <v>108</v>
       </c>
       <c r="B87" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C87" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D87" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E87" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>270</v>
+        <v>108</v>
       </c>
       <c r="B88" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C88" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D88" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E88" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="B89" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C89" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D89" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E89" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="B90" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C90" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D90" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E90" t="s">
         <v>181</v>
@@ -3907,67 +3973,67 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B91" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C91" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="D91" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E91" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="B92" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C92" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="D92" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E92" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B93" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C93" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="D93" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E93" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B94" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C94" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="D94" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E94" t="s">
         <v>181</v>
@@ -3975,101 +4041,101 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="B95" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C95" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="D95" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E95" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="B96" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C96" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="D96" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E96" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="B97" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C97" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D97" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E97" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>120</v>
+        <v>290</v>
       </c>
       <c r="B98" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C98" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="D98" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E98" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>120</v>
+        <v>294</v>
       </c>
       <c r="B99" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C99" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D99" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E99" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>120</v>
+        <v>295</v>
       </c>
       <c r="B100" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C100" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
       <c r="D100" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E100" t="s">
         <v>181</v>
@@ -4077,67 +4143,67 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B101" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C101" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="D101" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E101" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="B102" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C102" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="D102" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E102" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B103" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C103" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="D103" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E103" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B104" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C104" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="D104" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E104" t="s">
         <v>181</v>
@@ -4145,67 +4211,67 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B105" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C105" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="D105" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E105" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="B106" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C106" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="D106" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E106" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>291</v>
+        <v>130</v>
       </c>
       <c r="B107" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C107" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="D107" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E107" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B108" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C108" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="D108" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E108" t="s">
         <v>181</v>
@@ -4213,67 +4279,67 @@
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B109" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C109" t="s">
-        <v>295</v>
+        <v>308</v>
       </c>
       <c r="D109" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E109" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>294</v>
+        <v>307</v>
       </c>
       <c r="B110" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C110" t="s">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="D110" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E110" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>297</v>
+        <v>310</v>
       </c>
       <c r="B111" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C111" t="s">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="D111" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E111" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="B112" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C112" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="D112" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E112" t="s">
         <v>181</v>
@@ -4281,101 +4347,101 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>300</v>
+        <v>138</v>
       </c>
       <c r="B113" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C113" t="s">
-        <v>301</v>
+        <v>314</v>
       </c>
       <c r="D113" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E113" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>300</v>
+        <v>138</v>
       </c>
       <c r="B114" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="D114" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E114" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>303</v>
+        <v>316</v>
       </c>
       <c r="B115" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C115" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="D115" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E115" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="B116" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C116" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="D116" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E116" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="B117" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C117" t="s">
-        <v>307</v>
+        <v>320</v>
       </c>
       <c r="D117" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E117" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>308</v>
+        <v>321</v>
       </c>
       <c r="B118" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C118" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="D118" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E118" t="s">
         <v>181</v>
@@ -4383,67 +4449,67 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="B119" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C119" t="s">
-        <v>311</v>
+        <v>324</v>
       </c>
       <c r="D119" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E119" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>310</v>
+        <v>323</v>
       </c>
       <c r="B120" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C120" t="s">
-        <v>312</v>
+        <v>325</v>
       </c>
       <c r="D120" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E120" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B121" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C121" t="s">
-        <v>313</v>
+        <v>327</v>
       </c>
       <c r="D121" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E121" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="B122" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C122" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="D122" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E122" t="s">
         <v>181</v>
@@ -4451,101 +4517,101 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
+        <v>330</v>
+      </c>
+      <c r="B123" t="s">
         <v>145</v>
       </c>
-      <c r="B123" t="s">
-        <v>144</v>
-      </c>
       <c r="C123" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="D123" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E123" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
+        <v>330</v>
+      </c>
+      <c r="B124" t="s">
         <v>145</v>
       </c>
-      <c r="B124" t="s">
-        <v>144</v>
-      </c>
       <c r="C124" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="D124" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E124" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="B125" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C125" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="D125" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E125" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="B126" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C126" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="D126" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E126" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="B127" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C127" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="D127" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E127" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>317</v>
+        <v>336</v>
       </c>
       <c r="B128" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C128" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="D128" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E128" t="s">
         <v>181</v>
@@ -4553,101 +4619,101 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="B129" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C129" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="D129" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E129" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="B130" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C130" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="D130" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E130" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="B131" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C131" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="D131" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E131" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="B132" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C132" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="D132" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E132" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="B133" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C133" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="D133" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E133" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>323</v>
+        <v>343</v>
       </c>
       <c r="B134" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C134" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="D134" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E134" t="s">
         <v>181</v>
@@ -4655,67 +4721,67 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B135" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C135" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="D135" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E135" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B136" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C136" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="D136" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E136" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="B137" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C137" t="s">
-        <v>329</v>
+        <v>348</v>
       </c>
       <c r="D137" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E137" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="B138" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C138" t="s">
-        <v>330</v>
+        <v>349</v>
       </c>
       <c r="D138" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E138" t="s">
         <v>181</v>
@@ -4723,67 +4789,67 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
+        <v>350</v>
+      </c>
+      <c r="B139" t="s">
         <v>157</v>
       </c>
-      <c r="B139" t="s">
-        <v>156</v>
-      </c>
       <c r="C139" t="s">
-        <v>331</v>
+        <v>351</v>
       </c>
       <c r="D139" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E139" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
+        <v>350</v>
+      </c>
+      <c r="B140" t="s">
         <v>157</v>
       </c>
-      <c r="B140" t="s">
-        <v>156</v>
-      </c>
       <c r="C140" t="s">
-        <v>332</v>
+        <v>352</v>
       </c>
       <c r="D140" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E140" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
+        <v>353</v>
+      </c>
+      <c r="B141" t="s">
         <v>157</v>
       </c>
-      <c r="B141" t="s">
-        <v>156</v>
-      </c>
       <c r="C141" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="D141" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E141" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
+        <v>353</v>
+      </c>
+      <c r="B142" t="s">
         <v>157</v>
       </c>
-      <c r="B142" t="s">
-        <v>156</v>
-      </c>
       <c r="C142" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="D142" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E142" t="s">
         <v>181</v>
@@ -4791,33 +4857,33 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
+        <v>356</v>
+      </c>
+      <c r="B143" t="s">
         <v>161</v>
       </c>
-      <c r="B143" t="s">
-        <v>160</v>
-      </c>
       <c r="C143" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="D143" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E143" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>356</v>
+      </c>
+      <c r="B144" t="s">
         <v>161</v>
       </c>
-      <c r="B144" t="s">
-        <v>160</v>
-      </c>
       <c r="C144" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="D144" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E144" t="s">
         <v>181</v>
